--- a/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,62 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>183523</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>04/09/2025</t>
+          <t>01/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>557178.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>44574.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>4900000.0</v>
+        <v>601752.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -377,57 +382,62 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>191563</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>08/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>1715967.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>85798.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>4950000.0</v>
+        <v>1801765.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +456,62 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVC</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>193839</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>12/09/2025</t>
+          <t>13/09/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>026078008681</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Hộ Kinh Doanh Trần Văn Cường (Phường 8)</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>209 đường Bình Giã, Phường Tam Thắng, Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>720000.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>72000.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>4980000.0</v>
+        <v>792000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,57 +530,62 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>196571</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>631714.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>31586.0</v>
+      </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>1200000.0</v>
+        <v>663300.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -584,57 +604,62 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MTL</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>199266</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>20/09/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>037165003053</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH CỬA HÀNG THÀNH LẬP 1</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>15A Kha Vạn Cân, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>1767314.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>141385.0</v>
+      </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>175000.0</v>
+        <v>1908699.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -653,57 +678,62 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MTH</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>203995</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>27/09/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>077094004359</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH HẢI SẢN TƯ HÀ</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>10 Hoàng Hoa Thám, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>2134599.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>111826.0</v>
+      </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>4450000.0</v>
+        <v>2246425.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -727,54 +757,57 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MCM</t>
+          <t>C25MVT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>631775</t>
+          <t>203996</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>03/09/2025</t>
+          <t>27/09/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3500817878</t>
+          <t>0302249586-009</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
+          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
+DICH VU KY THUAT H &amp; V</t>
         </is>
       </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>183518.53</v>
+        <v>1204545.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>14681.47</v>
-      </c>
-      <c r="N13" s="13"/>
+        <v>120455.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O13" s="13" t="n">
-        <v>198200.0</v>
+        <v>1325000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -793,59 +826,57 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MCM</t>
+          <t>C25MKT</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>638812</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>06/09/2025</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3500817878</t>
+          <t>077172004159</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
+          <t>HỘ KINH DOANH HOÀNG THỊ KIM THUẦN</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>38 đường Đồng Khởi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>Công ty Cổ phần Đầu tư Xây dựng Thương mại Dịch vụ Kỹ thuật H &amp; V</t>
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13" t="n">
-        <v>71314.29</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>3565.71</v>
-      </c>
-      <c r="N14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O14" s="13" t="n">
-        <v>74880.0</v>
+        <v>2.14035E7</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -869,54 +900,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MCM</t>
+          <t>C25MSF</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>648633</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>28/09/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3500817878</t>
+          <t>3502469464</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
+          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>627790.51</v>
+        <v>1514286.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>31389.49</v>
-      </c>
-      <c r="N15" s="13"/>
+        <v>75714.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O15" s="13" t="n">
-        <v>659180.0</v>
+        <v>1590000.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -940,54 +973,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MCM</t>
+          <t>C25MHN</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>648634</t>
+          <t>832</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>04/09/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3500817878</t>
+          <t>3502546101</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ SÀI GÒN - VŨNG TÀU</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Số 36 Nguyễn Thái Học, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>3502469834</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
         </is>
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>588703.73</v>
+        <v>564815.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>47096.27</v>
-      </c>
-      <c r="N16" s="13"/>
+        <v>45185.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O16" s="13" t="n">
-        <v>635800.0</v>
+        <v>610000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>

--- a/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
@@ -313,57 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>183523</t>
+          <t>774106</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>01/09/2025</t>
+          <t>08/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>557178.0</v>
+        <v>32407.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>44574.0</v>
+        <v>2593.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>601752.0</v>
+        <v>35000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -387,57 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MHM</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>191563</t>
+          <t>839902</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>17/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0110269067-014</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CHI NHÁNH BÀ RỊA - VŨNG TÀU – CÔNG TY CỔ PHẦN DI CHUYỂN XANH VÀ THÔNG MINH GSM</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>1169/7 Đường 30/4, Phường Phước Thắng, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CTY TNHH ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>1715967.0</v>
+        <v>32407.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>85798.0</v>
+        <v>2593.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1801765.0</v>
+        <v>35000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -461,12 +459,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MDB</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>193839</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -476,42 +474,41 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>0307926591</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ THƯƠNG MẠI CÔ BA VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 12C3 - 12C5 Dương Văn An, Phường Vũng Tàu, Thành phố Hồ Chí Minh,Việt Nam</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẠI LÝ TÀU BIỂN VŨNG TÀU</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>720000.0</v>
+        <v>762980.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>72000.0</v>
+        <v>62020.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>792000.0</v>
+        <v>825000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -535,57 +532,54 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MVT</t>
+          <t>C25MMD</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>196571</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>17/09/2025</t>
+          <t>13/09/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>0302249586-009</t>
+          <t>3500354108</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
+          <t>DOANH NGHIỆP TƯ NHÂN XĂNG DẦU LONG PHƯỚC</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
+          <t>Số 3 Trần Phú, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502217971</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
+          <t>Công Ty TNHH Đại Lý Tàu Biển Vũng Tàu</t>
         </is>
       </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>631714.0</v>
+        <v>1772185.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>31586.0</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>141775.0</v>
+      </c>
+      <c r="N10" s="13"/>
       <c r="O10" s="13" t="n">
-        <v>663300.0</v>
+        <v>1913960.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -593,443 +587,6 @@
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>199266</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>20/09/2025</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13" t="n">
-        <v>1767314.0</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>141385.0</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>1908699.0</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>203995</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>27/09/2025</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13" t="n">
-        <v>2134599.0</v>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>111826.0</v>
-      </c>
-      <c r="N12" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>2246425.0</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>C25MVT</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>203996</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>27/09/2025</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>0302249586-009</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH CÔNG TY TNHH MM MEGA MARKET (VIỆT NAM) TẠI TỈNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Đường 2 tháng 9 (Quốc lộ 51B), Khu phố 1, Phường Phước Thắng, Thành phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY CO PHAN DAU TU XAY DUNG THUONG MAI
-DICH VU KY THUAT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="13" t="n">
-        <v>1204545.0</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>120455.0</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>1325000.0</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>C25MKT</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>24/09/2025</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>077172004159</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH HOÀNG THỊ KIM THUẦN</t>
-        </is>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>38 đường Đồng Khởi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Công ty Cổ phần Đầu tư Xây dựng Thương mại Dịch vụ Kỹ thuật H &amp; V</t>
-        </is>
-      </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="13" t="n">
-        <v>2.14035E7</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>C25MSF</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>8699</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>28/09/2025</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>3502469464</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH PHÚ SỸ FOOD</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>Số 149 , Đường Ngô Đức Kế, Phường Tam Thắng,Thành Phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="13" t="n">
-        <v>1514286.0</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>75714.0</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>1590000.0</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>C25MHN</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>04/09/2025</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>3502546101</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ GAS HOÀNG NAM</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>C5-2/1 TT Đô Thị Chí Linh, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>3502245376</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="13" t="n">
-        <v>564815.0</v>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>45185.0</v>
-      </c>
-      <c r="N16" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="13" t="n">
-        <v>610000.0</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/9/HDDienTuMayTinhTien.xlsx
@@ -313,54 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MCV</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>2962033</t>
+          <t>2373968</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>13/09/2025</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0102721191-001</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN GOLDEN GATE - CHI NHÁNH MIỀN NAM</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Tầng 7 TTTM Gigamall, Số 240-242 Phạm Văn Đồng, Phường Hiệp Bình, TP Hồ Chí Minh</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>1330000.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>106400.0</v>
-      </c>
-      <c r="N7" s="13"/>
+        <v>74074.0</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O7" s="13" t="n">
-        <v>1436400.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -384,54 +386,56 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MUP</t>
+          <t>C25MLT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2374116</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>29/09/2025</t>
+          <t>02/09/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502312248</t>
+          <t>3600445359</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH UY PHONG TÂN THÀNH</t>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Đường Võ Thị Sáu, Phường Phú Mỹ, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502267355</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NGUYÊN KHANG</t>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
         </is>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>327273.0</v>
+        <v>925926.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>26182.0</v>
-      </c>
-      <c r="N8" s="13"/>
+        <v>74074.0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0.0</v>
+      </c>
       <c r="O8" s="13" t="n">
-        <v>373455.0</v>
+        <v>1000000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -439,6 +443,3145 @@
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>2383897</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2025</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K9" s="6"/>
+      <c r="L9" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2395516</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>2397760</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>04/09/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>2404652</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>879630.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>70370.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>2406720</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>05/09/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2413481</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>2413506</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>2413640</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>2423130</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>898148.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>71852.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>970000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2427357</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>07/09/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>898148.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>71852.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>970000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2432864</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>08/09/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2443721</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>2444139</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>2446243</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>09/09/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>2465431</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>11/09/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>2475599</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>12/09/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>879630.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>70370.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>2484316</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2488276</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>13/09/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>2493637</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>2495368</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>14/09/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>2505385</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>2506606</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>15/09/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>2516294</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>2519596</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>1018674.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>81494.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>1100168.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>2526348</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>17/09/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>2535950</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>18/09/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>2544062</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>2544256</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>2549032</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>879630.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>70370.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>2551418</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>2553860</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>2555609</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>20/09/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>2578259</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>22/09/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>2584731</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>23/09/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>2596023</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>2596301</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2597078</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>24/09/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>2605617</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>2608013</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>2610304</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>25/09/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>2618415</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>26/09/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>2637868</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>28/09/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MLT</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>2657910</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3600445359</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN THƯƠNG MẠI LONG THÀNH</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Số 286, Đường Lê Duẩn, Ấp Văn Hải, Xã Long Thành, Tỉnh Đồng Nai</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
